--- a/grupos/3ALCM - Estadisticos 20211.xlsx
+++ b/grupos/3ALCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="171">
   <si>
     <t>Materia</t>
   </si>
@@ -203,18 +203,18 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -230,21 +230,57 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
     <t>CAMARILLO</t>
   </si>
   <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LASTRE</t>
+  </si>
+  <si>
     <t>LARRINAGA</t>
   </si>
   <si>
+    <t>LIMA</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
@@ -254,6 +290,15 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
     <t>PLIEGO</t>
   </si>
   <si>
@@ -263,34 +308,88 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>TLECUILE</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>SORIA</t>
   </si>
   <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
     <t>SANTES</t>
   </si>
   <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LORENZO</t>
+    <t>LEON</t>
   </si>
   <si>
     <t>GOMEZ</t>
@@ -299,36 +398,102 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
     <t>CALIHUA</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
     <t>VANELY JUDITH</t>
   </si>
   <si>
+    <t>JOSSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>JOSE ISAIAS</t>
+  </si>
+  <si>
     <t>ARIEL</t>
   </si>
   <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
     <t>FERNANDA</t>
   </si>
   <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>JENIFER</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>VICTORINO</t>
+  </si>
+  <si>
     <t>GERMAN ISAI</t>
   </si>
   <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ATENEA</t>
+  </si>
+  <si>
     <t>GONZALO FEDERICO</t>
   </si>
   <si>
+    <t>MERARY MADAY</t>
+  </si>
+  <si>
     <t>GENARO RAFAEL</t>
   </si>
   <si>
     <t>JAQUELINE</t>
   </si>
   <si>
+    <t>CAROLINA</t>
+  </si>
+  <si>
+    <t>PERLA MARITZA</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>LISBETH ESMERALDA</t>
+  </si>
+  <si>
     <t>VICTOR GAMALIEL</t>
   </si>
   <si>
@@ -338,199 +503,34 @@
     <t>LAILA MANE</t>
   </si>
   <si>
+    <t>FERNANDO VADHIR</t>
+  </si>
+  <si>
+    <t>CYNTHIA AIDEE</t>
+  </si>
+  <si>
+    <t>FABIOLA</t>
+  </si>
+  <si>
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
     <t>ARLET</t>
   </si>
   <si>
+    <t>ROSARIO</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>SELINA</t>
+  </si>
+  <si>
+    <t>ERIKA</t>
+  </si>
+  <si>
     <t>JESUS URIEL</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LASTRE</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TLECUILE</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>JUAN ALBERTO</t>
-  </si>
-  <si>
-    <t>JENIFER</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>VICTORINO</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ATENEA</t>
-  </si>
-  <si>
-    <t>MERARY MADAY</t>
-  </si>
-  <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
-    <t>PERLA MARITZA</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>LISBETH ESMERALDA</t>
-  </si>
-  <si>
-    <t>FERNANDO VADHIR</t>
-  </si>
-  <si>
-    <t>CYNTHIA AIDEE</t>
-  </si>
-  <si>
-    <t>FABIOLA</t>
-  </si>
-  <si>
-    <t>ROSARIO</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>SELINA</t>
-  </si>
-  <si>
-    <t>ERIKA</t>
   </si>
 </sst>
 </file>
@@ -1034,22 +1034,22 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1076,10 +1076,10 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1111,22 +1111,22 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1153,16 +1153,16 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1182,10 +1182,10 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1197,13 +1197,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1236,10 +1236,10 @@
         <v>5</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1265,22 +1265,22 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1313,10 +1313,10 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1327,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -1336,10 +1336,10 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1351,13 +1351,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1381,19 +1381,19 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1425,16 +1425,16 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1461,16 +1461,16 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1481,7 +1481,7 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1496,22 +1496,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1535,13 +1535,13 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1573,22 +1573,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1615,7 +1615,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1624,7 +1624,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1635,7 +1635,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1644,10 +1644,10 @@
         <v>5</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1659,13 +1659,13 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1689,7 +1689,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1698,10 +1698,10 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1727,22 +1727,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1763,7 +1763,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1772,10 +1772,10 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1804,22 +1804,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1840,7 +1840,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1852,10 +1852,10 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1881,22 +1881,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1920,13 +1920,13 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>10</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1943,7 +1943,7 @@
         <v>8</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -1964,16 +1964,16 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1997,7 +1997,7 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -2006,10 +2006,10 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2035,22 +2035,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2112,22 +2112,22 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2157,13 +2157,13 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2189,22 +2189,22 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2228,19 +2228,19 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2266,22 +2266,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2305,7 +2305,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2328,7 +2328,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -2337,13 +2337,13 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2352,13 +2352,13 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2382,7 +2382,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2391,10 +2391,10 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2423,19 +2423,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2459,7 +2459,7 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2468,10 +2468,10 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2497,22 +2497,22 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2536,7 +2536,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2574,22 +2574,22 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2610,16 +2610,16 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2636,7 +2636,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2645,10 +2645,10 @@
         <v>5</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2657,16 +2657,16 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2690,19 +2690,19 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2728,22 +2728,22 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2767,7 +2767,7 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2790,7 +2790,7 @@
         <v>8</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -2802,25 +2802,25 @@
         <v>8</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2844,10 +2844,10 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2856,7 +2856,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2867,7 +2867,7 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -2876,10 +2876,10 @@
         <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2891,13 +2891,13 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2921,19 +2921,19 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>5</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2962,19 +2962,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3004,13 +3004,13 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3036,22 +3036,22 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3072,22 +3072,22 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>6</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3098,7 +3098,7 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -3107,10 +3107,10 @@
         <v>6</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3119,16 +3119,16 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3152,19 +3152,19 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>5</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3175,7 +3175,7 @@
         <v>8</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -3196,16 +3196,16 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3229,19 +3229,19 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>5</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3252,7 +3252,7 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -3261,10 +3261,10 @@
         <v>5</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3273,16 +3273,16 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3306,7 +3306,7 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -3315,10 +3315,10 @@
         <v>5</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3344,22 +3344,22 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3383,7 +3383,7 @@
         <v>9</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -3421,22 +3421,22 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3460,7 +3460,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3469,7 +3469,7 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3498,22 +3498,22 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3540,16 +3540,16 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>7</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3569,28 +3569,28 @@
         <v>8</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G37">
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3617,13 +3617,13 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>8</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3655,19 +3655,19 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3694,16 +3694,16 @@
         <v>6</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3729,22 +3729,22 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3768,13 +3768,13 @@
         <v>9</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>10</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>9</v>
@@ -3806,22 +3806,22 @@
         <v>10</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3842,16 +3842,16 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>8</v>
@@ -3883,22 +3883,22 @@
         <v>10</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3919,19 +3919,19 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>10</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y41">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>5</v>
       </c>
       <c r="C42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -3954,10 +3954,10 @@
         <v>6</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H42">
         <v>-1</v>
@@ -3966,16 +3966,16 @@
         <v>-1</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3999,19 +3999,19 @@
         <v>5</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V42">
         <v>5</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4076,30 +4076,30 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>69.23</v>
+        <v>74.36</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>25.64</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -4111,27 +4111,27 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>74.36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>25.64</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>25.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -4140,30 +4140,30 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>74.36</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>20.51</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>25.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -4172,19 +4172,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="G5">
-        <v>25.64</v>
+        <v>15.38</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -4216,7 +4216,7 @@
         <v>15.38</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4236,19 +4236,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G7">
-        <v>12.82</v>
+        <v>10.26</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4264,7 +4264,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4289,646 +4289,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920220</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920220</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920222</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920222</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920222</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920224</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920228</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920234</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920234</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920234</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920236</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920236</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920236</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920237</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920237</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920237</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920240</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920240</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920244</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920244</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920244</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920245</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920247</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920247</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920247</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920251</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920251</v>
-      </c>
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" t="s">
-        <v>106</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920251</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920252</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920259</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920259</v>
-      </c>
-      <c r="B32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" t="s">
-        <v>108</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920259</v>
-      </c>
-      <c r="B33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" t="s">
-        <v>108</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -4964,189 +4324,189 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920222</v>
+        <v>20330051920187</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920234</v>
+        <v>20330051920220</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920236</v>
+        <v>20330051920221</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920237</v>
+        <v>20330051920374</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920244</v>
+        <v>20330051920222</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920247</v>
+        <v>20330051920223</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920251</v>
+        <v>20330051920224</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920259</v>
+        <v>20330051920225</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920220</v>
+        <v>20330051920375</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920240</v>
+        <v>20330051920226</v>
       </c>
       <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
         <v>77</v>
       </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920224</v>
+        <v>20330051920227</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5154,61 +4514,61 @@
         <v>20330051920228</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920245</v>
+        <v>20330051920229</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920252</v>
+        <v>20330051920230</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920187</v>
+        <v>20330051920231</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
         <v>146</v>
@@ -5219,13 +4579,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920221</v>
+        <v>20330051920232</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
         <v>147</v>
@@ -5236,13 +4596,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920374</v>
+        <v>20330051920233</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
         <v>148</v>
@@ -5253,13 +4613,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920223</v>
+        <v>20330051920234</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
         <v>149</v>
@@ -5270,13 +4630,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920225</v>
+        <v>20330051920376</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
         <v>150</v>
@@ -5287,13 +4647,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920375</v>
+        <v>20330051920236</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
         <v>151</v>
@@ -5304,13 +4664,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920226</v>
+        <v>20330051920237</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
         <v>152</v>
@@ -5321,13 +4681,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920227</v>
+        <v>20330051920238</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
         <v>153</v>
@@ -5338,13 +4698,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920229</v>
+        <v>20330051920239</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>154</v>
@@ -5355,13 +4715,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920230</v>
+        <v>20330051920240</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
         <v>155</v>
@@ -5372,13 +4732,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920231</v>
+        <v>20330051920241</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
         <v>156</v>
@@ -5389,13 +4749,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920232</v>
+        <v>20330051920243</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
         <v>157</v>
@@ -5406,13 +4766,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920233</v>
+        <v>20330051920244</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
         <v>158</v>
@@ -5423,13 +4783,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920376</v>
+        <v>20330051920245</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
         <v>159</v>
@@ -5440,13 +4800,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920238</v>
+        <v>20330051920247</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
         <v>160</v>
@@ -5457,13 +4817,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920239</v>
+        <v>20330051920248</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
         <v>161</v>
@@ -5474,13 +4834,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920241</v>
+        <v>20330051920249</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
         <v>162</v>
@@ -5491,13 +4851,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920243</v>
+        <v>20330051920250</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
         <v>163</v>
@@ -5508,13 +4868,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920248</v>
+        <v>20330051920251</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
         <v>164</v>
@@ -5525,13 +4885,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920249</v>
+        <v>20330051920252</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D35" t="s">
         <v>165</v>
@@ -5542,13 +4902,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920250</v>
+        <v>20330051920253</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
         <v>166</v>
@@ -5559,13 +4919,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920253</v>
+        <v>20330051920256</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D37" t="s">
         <v>167</v>
@@ -5576,13 +4936,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>20330051920256</v>
+        <v>20330051920257</v>
       </c>
       <c r="B38" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
         <v>168</v>
@@ -5593,13 +4953,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>20330051920257</v>
+        <v>20330051920258</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
         <v>169</v>
@@ -5610,13 +4970,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>20330051920258</v>
+        <v>20330051920259</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
         <v>170</v>
@@ -5664,42 +5024,42 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920245</v>
+        <v>20330051920220</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920245</v>
+        <v>20330051920220</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>63</v>
@@ -5710,22 +5070,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920223</v>
+        <v>20330051920234</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
         <v>149</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5733,45 +5093,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920224</v>
+        <v>20330051920234</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920226</v>
+        <v>20330051920224</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5779,45 +5139,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920228</v>
+        <v>20330051920375</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920250</v>
+        <v>20330051920228</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5825,45 +5185,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920252</v>
+        <v>20330051920240</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920253</v>
+        <v>20330051920252</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <v>5</v>

--- a/grupos/3ALCM - Estadisticos 20211.xlsx
+++ b/grupos/3ALCM - Estadisticos 20211.xlsx
@@ -1114,7 +1114,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -1150,7 +1150,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>8</v>

--- a/grupos/3ALCM - Estadisticos 20211.xlsx
+++ b/grupos/3ALCM - Estadisticos 20211.xlsx
@@ -2882,7 +2882,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2918,7 +2918,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -3960,7 +3960,7 @@
         <v>5</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I42">
         <v>-1</v>
@@ -3996,7 +3996,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -4236,19 +4236,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>89.73999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="G7">
-        <v>10.26</v>
+        <v>5.13</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ALCM - Estadisticos 20211.xlsx
+++ b/grupos/3ALCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="171">
   <si>
     <t>Materia</t>
   </si>
@@ -203,19 +203,19 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>NC</t>
@@ -1052,22 +1052,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -1129,31 +1129,31 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>9</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -1188,13 +1188,13 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -1206,40 +1206,40 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>7</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1283,22 +1283,22 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1310,13 +1310,13 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1342,13 +1342,13 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1360,22 +1360,22 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1419,10 +1419,10 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>7</v>
@@ -1437,28 +1437,28 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1470,7 +1470,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1514,22 +1514,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1538,13 +1538,13 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1576,7 +1576,7 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>8</v>
@@ -1591,40 +1591,40 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>9</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1650,13 +1650,13 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -1668,22 +1668,22 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1692,10 +1692,10 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1733,7 +1733,7 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>5</v>
@@ -1745,25 +1745,25 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1772,7 +1772,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1807,7 +1807,7 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -1822,34 +1822,34 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1899,28 +1899,28 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1958,10 +1958,10 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -1976,37 +1976,37 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>8</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -2053,34 +2053,34 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2130,34 +2130,34 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>8</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2207,31 +2207,31 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>8</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2284,22 +2284,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2346,10 +2346,10 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -2361,22 +2361,22 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2385,13 +2385,13 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>6</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2420,13 +2420,13 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>8</v>
@@ -2438,34 +2438,34 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2515,22 +2515,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2592,22 +2592,22 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2616,7 +2616,7 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2651,10 +2651,10 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -2669,22 +2669,22 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -2699,7 +2699,7 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2746,22 +2746,22 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2808,7 +2808,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>8</v>
@@ -2823,22 +2823,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2856,7 +2856,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2885,10 +2885,10 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -2900,37 +2900,37 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U28">
         <v>5</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -2959,7 +2959,7 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2977,25 +2977,25 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -3007,10 +3007,10 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3042,7 +3042,7 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
         <v>9</v>
@@ -3054,34 +3054,34 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>8</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -3113,10 +3113,10 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>4</v>
@@ -3131,40 +3131,40 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>5</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3190,10 +3190,10 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>4</v>
@@ -3208,25 +3208,25 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3238,10 +3238,10 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3267,10 +3267,10 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -3285,25 +3285,25 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>5</v>
@@ -3315,7 +3315,7 @@
         <v>5</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3362,28 +3362,28 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>9</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -3439,22 +3439,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>8</v>
@@ -3466,10 +3466,10 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3516,37 +3516,37 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>8</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>7</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3593,37 +3593,37 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>8</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3652,7 +3652,7 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I38">
         <v>6</v>
@@ -3670,22 +3670,22 @@
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>8</v>
@@ -3694,10 +3694,10 @@
         <v>6</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3747,22 +3747,22 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>9</v>
@@ -3824,22 +3824,22 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -3854,7 +3854,7 @@
         <v>7</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y40">
         <v>10</v>
@@ -3901,28 +3901,28 @@
         <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>9</v>
       </c>
       <c r="U41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V41">
         <v>10</v>
@@ -3931,7 +3931,7 @@
         <v>10</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y41">
         <v>10</v>
@@ -3963,7 +3963,7 @@
         <v>7</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J42">
         <v>4</v>
@@ -3978,25 +3978,25 @@
         <v>5</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -4011,7 +4011,7 @@
         <v>5</v>
       </c>
       <c r="Y42">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4076,19 +4076,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>74.36</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G2">
-        <v>25.64</v>
+        <v>28.21</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -4108,19 +4108,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>74.36</v>
+        <v>82.05</v>
       </c>
       <c r="G3">
-        <v>25.64</v>
+        <v>17.95</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -4140,19 +4140,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>79.48999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="G4">
-        <v>20.51</v>
+        <v>15.38</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4172,19 +4172,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>84.62</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="G5">
-        <v>15.38</v>
+        <v>12.82</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -4204,19 +4204,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G6">
-        <v>15.38</v>
+        <v>10.26</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -4236,16 +4236,16 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>94.87</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G7">
-        <v>5.13</v>
+        <v>10.26</v>
       </c>
       <c r="H7">
         <v>7.9</v>
@@ -4992,7 +4992,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5024,22 +5024,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920220</v>
+        <v>20330051920228</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5047,22 +5047,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920220</v>
+        <v>20330051920228</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5070,16 +5070,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920234</v>
+        <v>20330051920244</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920234</v>
+        <v>20330051920244</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5116,22 +5116,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920224</v>
+        <v>20330051920220</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5139,19 +5139,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920375</v>
+        <v>20330051920223</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>61</v>
@@ -5162,16 +5162,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920228</v>
+        <v>20330051920234</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5203,29 +5203,6 @@
         <v>60</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920252</v>
-      </c>
-      <c r="B10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>
